--- a/input/missing-products/1.xlsx
+++ b/input/missing-products/1.xlsx
@@ -1,156 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emois\IdeaProjects\PARSERS\product-importer\input\missing-products\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\webuser_3\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C49C32-E033-400A-9B62-CD9D23B054D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" refMode="R1C1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Message</t>
   </si>
   <si>
-    <t>Ячейка E8, Определение продукта роза арт деко не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E9, Определение продукта роза арт новеа не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E17, Определение продукта роза брауни мун не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E44, Определение продукта роза крашеная аврора не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E45, Определение продукта роза крашеная брайт скай не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E46, Определение продукта роза крашеная лайт блю не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E47, Определение продукта роза крашеная свит баг не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E48, Определение продукта роза крашеная симпати не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E49, Определение продукта роза крашеная фантазия блю пинк не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E51, Определение продукта роза крем джульет не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E61, Определение продукта роза мадмуазель не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E70, Определение продукта роза мокка не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E108, Определение продукта роза свит ай не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E109, Определение продукта роза свит ай не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E110, Определение продукта роза свит мента не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E136, Определение продукта роза экзотик минт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E146, Определение продукта роза юи гарден не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E157, Определение продукта роза ноель не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E192, Определение продукта роза ветвистая джульета лайт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E193, Определение продукта роза ветвистая джульета лайт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E197, Определение продукта роза ветвистая доминики не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E212, Определение продукта роза ветвистая мэнсфилд парк пинк не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E216, Определение продукта роза ветвистая ориджинал бомбастик не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E258, Определение продукта гвоздика мини сиреневая китай, шт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E265, Определение продукта гвоздика харизма не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E309, Определение продукта хризантема пиони белая китай, шт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E339, Определение продукта гербера игольчатая крем не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E364, Определение продукта гладиолус белый китай, шт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E365, Определение продукта гладиолус розовый китай, шт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E378, Определение продукта дельфиниум белый китай, шт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E380, Определение продукта дельфиниум лавандовый не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E394, Определение продукта кампанула зелено-белая не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E400, Определение продукта леукандендрон айоба африка не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E402, Определение продукта леукоспернум крашенный красный не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E426, Определение продукта пион лемон шифон не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E433, Определение продукта ранункулус баттерфляй розовый не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E454, Определение продукта эрингиум мики китай, пуч не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E461, Определение продукта эустома светло-розовая биг сан не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E465, Определение продукта хризалидоварпус китай, пуч не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>вцвцвцвцв</t>
-  </si>
-  <si>
-    <t>уцуцуцуцуцу</t>
+    <t>Ячейка E35, Определение продукта роза крашеная черная планета не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E49, Определение продукта роза матча не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E164, Определение продукта роза ветвистая викториан классик nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E184, Определение продукта роза ветвистая пьяно красная nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E185, Определение продукта роза ветвистая резиденс nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E194, Определение продукта роза ветвистая сноуфлейк nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E195, Определение продукта роза ветвистая сноуфлейк nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E207, Определение продукта гвоздика мати сиреневая не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E211, Определение продукта питтоспорум ралфи не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E243, Определение продукта хризантема пингпонг розовая китай, шт не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E261, Определение продукта анигозантус зеленый не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E262, Определение продукта антиринум белый армения не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E263, Определение продукта антиринум желтый армения не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E264, Определение продукта антиринум красный армения не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E266, Определение продукта антиринум розовый армения не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E267, Определение продукта арункус не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E286, Определение продукта гербера светло-розовая не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E335, Определение продукта пион флоренс никольс не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E339, Определение продукта скабиоза стеллата не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E343, Определение продукта эрика розовая не найдено или не связано с предоставленными складами</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -216,7 +154,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -228,7 +166,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -275,6 +213,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -310,6 +265,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -461,8 +433,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -570,111 +542,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>39</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/input/missing-products/1.xlsx
+++ b/input/missing-products/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\webuser_3\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C49C32-E033-400A-9B62-CD9D23B054D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2691B7E9-4362-4347-8287-BB9267663F15}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,69 +20,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Message</t>
   </si>
   <si>
-    <t>Ячейка E35, Определение продукта роза крашеная черная планета не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E49, Определение продукта роза матча не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E164, Определение продукта роза ветвистая викториан классик nl не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E184, Определение продукта роза ветвистая пьяно красная nl не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E185, Определение продукта роза ветвистая резиденс nl не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E194, Определение продукта роза ветвистая сноуфлейк nl не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E195, Определение продукта роза ветвистая сноуфлейк nl не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E207, Определение продукта гвоздика мати сиреневая не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E211, Определение продукта питтоспорум ралфи не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E243, Определение продукта хризантема пингпонг розовая китай, шт не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E261, Определение продукта анигозантус зеленый не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E262, Определение продукта антиринум белый армения не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E263, Определение продукта антиринум желтый армения не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E264, Определение продукта антиринум красный армения не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E266, Определение продукта антиринум розовый армения не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E267, Определение продукта арункус не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E286, Определение продукта гербера светло-розовая не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E335, Определение продукта пион флоренс никольс не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E339, Определение продукта скабиоза стеллата не найдено или не связано с предоставленными складами</t>
-  </si>
-  <si>
-    <t>Ячейка E343, Определение продукта эрика розовая не найдено или не связано с предоставленными складами</t>
+    <t>Ячейка E149, Определение продукта роза беллевью не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E188, Определение продукта роза ветвистая азор nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E190, Определение продукта роза ветвистая бачелор nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E196, Определение продукта роза ветвистая вуетте nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E201, Определение продукта роза ветвистая дарлингтон nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E212, Определение продукта роза ветвистая нанди не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E222, Определение продукта роза ветвистая рубикон nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E225, Определение продукта роза ветвистая салинеро nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E226, Определение продукта роза ветвистая саммер дэнс nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E227, Определение продукта роза ветвистая саммер роуз nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E228, Определение продукта роза ветвистая сансет меджик nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E232, Определение продукта роза ветвистая сильвия пинк nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E243, Определение продукта роза ветвистая хэппи вейдинг nl не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E246, Определение продукта роза ветвистая ёрс энд фаер не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E264, Определение продукта гвоздика мини персиковая не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E315, Определение продукта антиринум сильвер не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E316, Определение продукта антуриум блэк лав не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E352, Определение продукта калла самур не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E353, Определение продукта калла эскейп не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E355, Определение продукта кампанула зелено-розовая не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E357, Определение продукта котинус не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E371, Определение продукта матиола лавандовая не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E375, Определение продукта мята, пуч не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E385, Определение продукта пион авис не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E386, Определение продукта пион аивори белый не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E395, Определение продукта ранункулюс белый тесса не найдено или не связано с предоставленными складами</t>
+  </si>
+  <si>
+    <t>Ячейка E396, Определение продукта ранункулюс ханой тесса не найдено или не связано с предоставленными складами</t>
   </si>
 </sst>
 </file>
@@ -434,8 +455,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="122.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -542,6 +566,41 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
